--- a/amircup26_fa.xlsx
+++ b/amircup26_fa.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\drs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{153C1D64-A304-4887-BA2E-0700418CD9C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16F044E6-A9E9-4029-B919-772B8700EC74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-1740" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21780" yWindow="-675" windowWidth="20625" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Contact List - 2026" sheetId="1" r:id="rId1"/>
     <sheet name="Comments" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Contact List - 2026'!$A$1:$J$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Contact List - 2026'!$A$1:$K$53</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="243">
   <si>
     <t>Number</t>
   </si>
@@ -786,13 +786,19 @@
   </si>
   <si>
     <t>HOS - Hospitality</t>
+  </si>
+  <si>
+    <t>sc</t>
+  </si>
+  <si>
+    <t>type</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -858,12 +864,6 @@
       <u/>
       <sz val="10"/>
       <color theme="10"/>
-      <name val="Verdana"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
       <name val="Verdana"/>
       <family val="2"/>
     </font>
@@ -1287,7 +1287,7 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1308,9 +1308,7 @@
     <xf numFmtId="0" fontId="7" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1652,10 +1650,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
+  <sheetPr filterMode="1">
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:J53"/>
+  <dimension ref="A1:L53"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" hidden="1"/>
@@ -1668,9 +1666,10 @@
     <col min="8" max="8" width="25.28515625" hidden="1" customWidth="1"/>
     <col min="9" max="9" width="21.42578125" hidden="1" customWidth="1"/>
     <col min="10" max="10" width="47.42578125" customWidth="1"/>
+    <col min="12" max="12" width="62.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1701,8 +1700,11 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" s="4" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="K1" s="1" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" s="4" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="b">
         <v>1</v>
       </c>
@@ -1733,8 +1735,15 @@
       <c r="J2" s="5" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" s="4" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="K2" s="70" t="s">
+        <v>241</v>
+      </c>
+      <c r="L2" s="4" t="e">
+        <f>LEFT(D1,FIND(CHAR(10),D1)-1)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" s="4" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="b">
         <v>1</v>
       </c>
@@ -1765,8 +1774,11 @@
       <c r="J3" s="5" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" s="4" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="K3" s="70" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" s="4" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
       <c r="B4" s="6" t="s">
         <v>20</v>
@@ -1795,8 +1807,11 @@
       <c r="J4" s="6" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" s="4" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="K4" s="70" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" s="4" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" s="5" t="s">
         <v>27</v>
@@ -1823,8 +1838,11 @@
       <c r="J5" s="5" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" s="4" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="K5" s="70" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" s="4" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
       <c r="B6" s="5" t="s">
         <v>33</v>
@@ -1852,7 +1870,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:10" s="4" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" s="4" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="b">
         <v>1</v>
       </c>
@@ -1884,7 +1902,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="8" spans="1:10" s="4" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" s="4" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="b">
         <v>1</v>
       </c>
@@ -1915,8 +1933,11 @@
       <c r="J8" s="5" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" s="49" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="K8" s="70" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" s="49" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="47"/>
       <c r="B9" s="52" t="s">
         <v>48</v>
@@ -1946,7 +1967,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="10" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="b">
         <v>1</v>
       </c>
@@ -1976,7 +1997,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="11" spans="1:10" s="4" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" s="4" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="5" t="s">
         <v>59</v>
@@ -2005,8 +2026,11 @@
       <c r="J11" s="5" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" s="4" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="K11" s="70" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" s="4" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="5" t="s">
         <v>65</v>
@@ -2035,8 +2059,11 @@
       <c r="J12" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" s="4" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="K12" s="70" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" s="4" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="32" t="s">
         <v>68</v>
@@ -2063,8 +2090,11 @@
       <c r="J13" s="5" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" s="4" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="K13" s="4" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" s="4" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="b">
         <v>1</v>
       </c>
@@ -2091,8 +2121,11 @@
       <c r="J14" s="5" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K14" s="70" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="b">
         <v>1</v>
       </c>
@@ -2122,7 +2155,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="16" spans="1:10" s="4" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" s="4" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
       <c r="B16" s="58" t="s">
         <v>83</v>
@@ -2152,7 +2185,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="17" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3"/>
       <c r="B17" s="6" t="s">
         <v>88</v>
@@ -2180,7 +2213,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="18" spans="1:10" s="4" customFormat="1" ht="51" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" s="4" customFormat="1" ht="51" x14ac:dyDescent="0.25">
       <c r="A18" s="3"/>
       <c r="B18" s="6" t="s">
         <v>94</v>
@@ -2209,8 +2242,11 @@
       <c r="J18" s="6" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="19" spans="1:10" s="4" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="K18" s="70" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" s="4" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A19" s="3"/>
       <c r="B19" s="6" t="s">
         <v>99</v>
@@ -2239,8 +2275,11 @@
       <c r="J19" s="6" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" s="4" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="K19" s="70" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" s="4" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A20" s="3"/>
       <c r="B20" s="6" t="s">
         <v>104</v>
@@ -2269,8 +2308,11 @@
       <c r="J20" s="6" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="21" spans="1:10" s="4" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="K20" s="70" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" s="4" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A21" s="3"/>
       <c r="B21" s="6" t="s">
         <v>109</v>
@@ -2299,8 +2341,11 @@
       <c r="J21" s="6" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="22" spans="1:10" s="4" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="K21" s="70" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" s="4" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A22" s="3"/>
       <c r="B22" s="6" t="s">
         <v>114</v>
@@ -2329,8 +2374,11 @@
       <c r="J22" s="6" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="23" spans="1:10" s="4" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="K22" s="70" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" s="4" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A23" s="3"/>
       <c r="B23" s="6" t="s">
         <v>119</v>
@@ -2359,8 +2407,11 @@
       <c r="J23" s="6" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="24" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K23" s="70" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3"/>
       <c r="B24" s="6" t="s">
         <v>124</v>
@@ -2390,7 +2441,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="25" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3"/>
       <c r="B25" s="6" t="s">
         <v>129</v>
@@ -2418,7 +2469,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="26" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3"/>
       <c r="B26" s="6" t="s">
         <v>134</v>
@@ -2446,7 +2497,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="27" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3"/>
       <c r="B27" s="6" t="s">
         <v>134</v>
@@ -2474,7 +2525,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="28" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3"/>
       <c r="B28" s="6" t="s">
         <v>141</v>
@@ -2502,7 +2553,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="29" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3"/>
       <c r="B29" s="6" t="s">
         <v>141</v>
@@ -2528,7 +2579,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="30" spans="1:10" s="4" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" s="4" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A30" s="3"/>
       <c r="B30" s="6" t="s">
         <v>148</v>
@@ -2536,7 +2587,7 @@
       <c r="C30" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="D30" s="70" t="s">
+      <c r="D30" s="60" t="s">
         <v>236</v>
       </c>
       <c r="E30" s="6" t="s">
@@ -2557,8 +2608,11 @@
       <c r="J30" s="6" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="31" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K30" s="70" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3"/>
       <c r="B31" s="6" t="s">
         <v>153</v>
@@ -2586,7 +2640,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="32" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3"/>
       <c r="B32" s="6" t="s">
         <v>158</v>
@@ -2614,7 +2668,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="33" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3"/>
       <c r="B33" s="6" t="s">
         <v>158</v>
@@ -2642,7 +2696,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="34" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3"/>
       <c r="B34" s="6" t="s">
         <v>158</v>
@@ -2670,7 +2724,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="35" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3"/>
       <c r="B35" s="6" t="s">
         <v>158</v>
@@ -2698,7 +2752,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="36" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3"/>
       <c r="B36" s="6" t="s">
         <v>158</v>
@@ -2726,7 +2780,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="37" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="b">
         <v>1</v>
       </c>
@@ -2748,7 +2802,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="38" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3"/>
       <c r="B38" s="6" t="s">
         <v>175</v>
@@ -2770,7 +2824,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="b">
         <v>1</v>
       </c>
@@ -2800,7 +2854,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="B40" s="10" t="s">
         <v>184</v>
       </c>
@@ -2827,7 +2881,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B41" s="11" t="s">
         <v>188</v>
       </c>
@@ -2853,8 +2907,11 @@
       <c r="J41" s="12" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K41" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B42" s="11" t="s">
         <v>192</v>
       </c>
@@ -2877,7 +2934,7 @@
       </c>
       <c r="J42" s="12"/>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B43" s="11" t="s">
         <v>192</v>
       </c>
@@ -2898,7 +2955,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B44" s="28" t="s">
         <v>192</v>
       </c>
@@ -2923,7 +2980,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B45" s="11" t="s">
         <v>192</v>
       </c>
@@ -2948,7 +3005,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="46" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3"/>
       <c r="B46" s="32" t="s">
         <v>202</v>
@@ -2968,7 +3025,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="3"/>
       <c r="B47" s="9"/>
       <c r="C47" s="34" t="s">
@@ -2984,7 +3041,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="48" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3"/>
       <c r="B48" s="6"/>
       <c r="C48" s="7" t="s">
@@ -3000,7 +3057,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="3"/>
       <c r="B49" s="6"/>
       <c r="C49" s="6" t="s">
@@ -3016,7 +3073,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3"/>
       <c r="B50" s="6"/>
       <c r="C50" s="6" t="s">
@@ -3034,7 +3091,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="3"/>
       <c r="B51" s="6"/>
       <c r="C51" s="6" t="s">
@@ -3050,7 +3107,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3"/>
       <c r="B52" s="8"/>
       <c r="C52" s="8" t="s">
@@ -3066,7 +3123,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B53" s="22"/>
       <c r="C53" s="22" t="s">
         <v>215</v>
@@ -3082,7 +3139,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J53" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:K53" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="10">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+  </autoFilter>
   <hyperlinks>
     <hyperlink ref="G4" r:id="rId1" xr:uid="{2E560536-0AE7-419F-ABE4-50D2FA845D20}"/>
     <hyperlink ref="G3" r:id="rId2" xr:uid="{96B27229-9D47-421A-989A-75809216E45C}"/>
@@ -3153,6 +3216,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E13F088644BD57448CD339F5F02EB6EB" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e6345697ef3e092e87686242534e6f53">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2028cff8-799a-4601-992e-254126270846" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b8eb01b9d2e60ed4a8fc2e591c44cb4a" ns2:_="">
     <xsd:import namespace="2028cff8-799a-4601-992e-254126270846"/>
@@ -3296,15 +3368,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -3312,6 +3375,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{064CFCA9-8063-4C95-AFAA-DCF9DF90C564}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7E25C660-A62A-4BF5-8559-541F143505EF}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3325,14 +3396,6 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{064CFCA9-8063-4C95-AFAA-DCF9DF90C564}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
